--- a/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C232DF3E-D1D8-4A92-A9D1-3410996CACF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{064BD0C1-D4BA-4287-9517-DF2FDDAC1D24}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC640E7-16D0-43A4-B0CD-C8069C18661E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48AFFD74-4494-4330-B72C-FBDF21036357}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FBF5F67-6051-4F7D-A384-0FEE4AB6FEA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFE483F4-DE0F-4F13-9466-D3B176B38376}"/>
 </file>